--- a/csv/model/DCC/formula_DCC_BC.xlsx
+++ b/csv/model/DCC/formula_DCC_BC.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,12 +440,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:X533"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Load factor</t>
+          <t>multiplier_load_factor</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7910,7 +7910,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -10238,7 +10238,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10753,7 +10753,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -12385,7 +12385,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12854,7 +12854,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -13317,7 +13317,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -13653,7 +13653,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -14283,7 +14283,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M206" t="n">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M207" t="n">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M208" t="n">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M209" t="n">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M210" t="n">
@@ -15053,7 +15053,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M211" t="n">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M212" t="n">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M213" t="n">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M214" t="n">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M215" t="n">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M216" t="n">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M217" t="n">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M218" t="n">
@@ -15613,7 +15613,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M219" t="n">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M220" t="n">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M221" t="n">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M222" t="n">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M223" t="n">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M224" t="n">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M225" t="n">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M226" t="n">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M227" t="n">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M228" t="n">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M229" t="n">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M230" t="n">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M231" t="n">
@@ -16523,7 +16523,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M232" t="n">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M233" t="n">
@@ -16663,7 +16663,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M234" t="n">
@@ -16733,7 +16733,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M235" t="n">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M236" t="n">
@@ -16873,7 +16873,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M237" t="n">
@@ -16943,7 +16943,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M238" t="n">
@@ -17013,7 +17013,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M239" t="n">
@@ -17083,7 +17083,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M240" t="n">
@@ -17153,7 +17153,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M241" t="n">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M242" t="n">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M243" t="n">
@@ -17363,7 +17363,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M244" t="n">
@@ -17433,7 +17433,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M245" t="n">
@@ -17503,7 +17503,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M246" t="n">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="M247" t="n">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M248" t="n">
@@ -17713,7 +17713,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M249" t="n">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M250" t="n">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M251" t="n">
@@ -17923,7 +17923,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M252" t="n">
@@ -17993,7 +17993,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M253" t="n">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M254" t="n">
@@ -18133,7 +18133,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M255" t="n">
@@ -18203,7 +18203,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M256" t="n">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M257" t="n">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M258" t="n">
@@ -18413,7 +18413,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M259" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M260" t="n">
@@ -18553,7 +18553,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M261" t="n">
@@ -18623,7 +18623,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M262" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M263" t="n">
@@ -18763,7 +18763,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M264" t="n">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M265" t="n">
@@ -18903,7 +18903,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M266" t="n">
@@ -18973,7 +18973,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M267" t="n">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M268" t="n">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M269" t="n">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M270" t="n">
@@ -19253,7 +19253,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M271" t="n">
@@ -19323,7 +19323,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M272" t="n">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M273" t="n">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M274" t="n">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M275" t="n">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M276" t="n">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M277" t="n">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M278" t="n">
@@ -19813,7 +19813,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M279" t="n">
@@ -19883,7 +19883,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M280" t="n">
@@ -19953,7 +19953,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M281" t="n">
@@ -20023,7 +20023,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M282" t="n">
@@ -20093,7 +20093,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M283" t="n">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M284" t="n">
@@ -20233,7 +20233,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M285" t="n">
@@ -20303,7 +20303,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M286" t="n">
@@ -20373,7 +20373,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M287" t="n">
@@ -20443,7 +20443,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M288" t="n">
@@ -20513,7 +20513,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="M289" t="n">
@@ -20583,7 +20583,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M290" t="n">
@@ -20653,7 +20653,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M291" t="n">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M292" t="n">
@@ -20793,7 +20793,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M293" t="n">
@@ -20863,7 +20863,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M294" t="n">
@@ -20933,7 +20933,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M295" t="n">
@@ -21003,7 +21003,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M296" t="n">
@@ -21073,7 +21073,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M297" t="n">
@@ -21143,7 +21143,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M298" t="n">
@@ -21213,7 +21213,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M299" t="n">
@@ -21283,7 +21283,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M300" t="n">
@@ -21353,7 +21353,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M301" t="n">
@@ -21423,7 +21423,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M302" t="n">
@@ -21493,7 +21493,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M303" t="n">
@@ -21563,7 +21563,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M304" t="n">
@@ -21633,7 +21633,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M305" t="n">
@@ -21703,7 +21703,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M306" t="n">
@@ -21773,7 +21773,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M307" t="n">
@@ -21843,7 +21843,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M308" t="n">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M309" t="n">
@@ -21983,7 +21983,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M310" t="n">
@@ -22053,7 +22053,7 @@
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M311" t="n">
@@ -22123,7 +22123,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M312" t="n">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M313" t="n">
@@ -22263,7 +22263,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M314" t="n">
@@ -22333,7 +22333,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M315" t="n">
@@ -22403,7 +22403,7 @@
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M316" t="n">
@@ -22473,7 +22473,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M317" t="n">
@@ -22543,7 +22543,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M318" t="n">
@@ -22613,7 +22613,7 @@
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M319" t="n">
@@ -22683,7 +22683,7 @@
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M320" t="n">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M321" t="n">
@@ -22823,7 +22823,7 @@
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M322" t="n">
@@ -22893,7 +22893,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M323" t="n">
@@ -22963,7 +22963,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M324" t="n">
@@ -23033,7 +23033,7 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M325" t="n">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M326" t="n">
@@ -23173,7 +23173,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M327" t="n">
@@ -23243,7 +23243,7 @@
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M328" t="n">
@@ -23313,7 +23313,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M329" t="n">
@@ -23383,7 +23383,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M330" t="n">
@@ -23453,7 +23453,7 @@
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="M331" t="n">
@@ -23523,7 +23523,7 @@
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M332" t="n">
@@ -23593,7 +23593,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M333" t="n">
@@ -23663,7 +23663,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M334" t="n">
@@ -23733,7 +23733,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M335" t="n">
@@ -23803,7 +23803,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M336" t="n">
@@ -23873,7 +23873,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M337" t="n">
@@ -23943,7 +23943,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M338" t="n">
@@ -24013,7 +24013,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M339" t="n">
@@ -24083,7 +24083,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M340" t="n">
@@ -24153,7 +24153,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M341" t="n">
@@ -24223,7 +24223,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M342" t="n">
@@ -24293,7 +24293,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M343" t="n">
@@ -24363,7 +24363,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M344" t="n">
@@ -24433,7 +24433,7 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M345" t="n">
@@ -24503,7 +24503,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M346" t="n">
@@ -24573,7 +24573,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M347" t="n">
@@ -24643,7 +24643,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M348" t="n">
@@ -24713,7 +24713,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M349" t="n">
@@ -24783,7 +24783,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M350" t="n">
@@ -24853,7 +24853,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M351" t="n">
@@ -24923,7 +24923,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M352" t="n">
@@ -24993,7 +24993,7 @@
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M353" t="n">
@@ -25063,7 +25063,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M354" t="n">
@@ -25133,7 +25133,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M355" t="n">
@@ -25203,7 +25203,7 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M356" t="n">
@@ -25273,7 +25273,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M357" t="n">
@@ -25343,7 +25343,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M358" t="n">
@@ -25413,7 +25413,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M359" t="n">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M360" t="n">
@@ -25553,7 +25553,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M361" t="n">
@@ -25623,7 +25623,7 @@
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M362" t="n">
@@ -25693,7 +25693,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M363" t="n">
@@ -25763,7 +25763,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M364" t="n">
@@ -25833,7 +25833,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M365" t="n">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M366" t="n">
@@ -25973,7 +25973,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M367" t="n">
@@ -26043,7 +26043,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M368" t="n">
@@ -26113,7 +26113,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M369" t="n">
@@ -26183,7 +26183,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M370" t="n">
@@ -26253,7 +26253,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M371" t="n">
@@ -26323,7 +26323,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M372" t="n">
@@ -26393,7 +26393,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="M373" t="n">
@@ -26463,7 +26463,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -26505,7 +26505,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -26595,7 +26595,7 @@
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -26685,7 +26685,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -26775,7 +26775,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L378" t="inlineStr">
@@ -26865,7 +26865,7 @@
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L380" t="inlineStr">
@@ -27002,7 +27002,7 @@
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -27092,7 +27092,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -27183,7 +27183,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -27273,7 +27273,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -27315,7 +27315,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -27405,7 +27405,7 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -27495,7 +27495,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -27586,7 +27586,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -27676,7 +27676,7 @@
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -27718,7 +27718,7 @@
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -27803,7 +27803,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -27888,7 +27888,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L392" t="inlineStr">
@@ -27979,7 +27979,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
@@ -28064,7 +28064,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -28106,7 +28106,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -28191,7 +28191,7 @@
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
@@ -28276,7 +28276,7 @@
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
@@ -28367,7 +28367,7 @@
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
@@ -28452,7 +28452,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -28499,7 +28499,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L400" t="inlineStr">
@@ -28589,7 +28589,7 @@
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L401" t="inlineStr">
@@ -28679,7 +28679,7 @@
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L402" t="inlineStr">
@@ -28770,7 +28770,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L403" t="inlineStr">
@@ -28860,7 +28860,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -28992,7 +28992,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -29082,7 +29082,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L408" t="inlineStr">
@@ -29263,7 +29263,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -29305,7 +29305,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -29485,7 +29485,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -29576,7 +29576,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L413" t="inlineStr">
@@ -29666,7 +29666,7 @@
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -29708,7 +29708,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
@@ -29798,7 +29798,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
@@ -29888,7 +29888,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
@@ -29979,7 +29979,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L418" t="inlineStr">
@@ -30069,7 +30069,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -30111,7 +30111,7 @@
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L420" t="inlineStr">
@@ -30196,7 +30196,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
@@ -30286,7 +30286,7 @@
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L422" t="inlineStr">
@@ -30377,7 +30377,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
@@ -30467,7 +30467,7 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -30509,7 +30509,7 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L425" t="inlineStr">
@@ -30594,7 +30594,7 @@
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
@@ -30684,7 +30684,7 @@
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -30775,7 +30775,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L428" t="inlineStr">
@@ -30865,7 +30865,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -30907,7 +30907,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L430" t="inlineStr">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
@@ -31082,7 +31082,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
@@ -31173,7 +31173,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L433" t="inlineStr">
@@ -31263,7 +31263,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -31305,7 +31305,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L435" t="inlineStr">
@@ -31390,7 +31390,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L436" t="inlineStr">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L437" t="inlineStr">
@@ -31571,7 +31571,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L438" t="inlineStr">
@@ -31661,7 +31661,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -31703,7 +31703,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
@@ -31788,7 +31788,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L441" t="inlineStr">
@@ -31878,7 +31878,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L442" t="inlineStr">
@@ -31969,7 +31969,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L443" t="inlineStr">
@@ -32059,7 +32059,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -32101,7 +32101,7 @@
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L445" t="inlineStr">
@@ -32186,7 +32186,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
@@ -32271,7 +32271,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
@@ -32362,7 +32362,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L448" t="inlineStr">
@@ -32447,7 +32447,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -32489,7 +32489,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L450" t="inlineStr">
@@ -32574,7 +32574,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L451" t="inlineStr">
@@ -32659,7 +32659,7 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -32750,7 +32750,7 @@
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L453" t="inlineStr">
@@ -32835,7 +32835,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -32877,7 +32877,7 @@
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L455" t="inlineStr">
@@ -32962,7 +32962,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L456" t="inlineStr">
@@ -33047,7 +33047,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L457" t="inlineStr">
@@ -33138,7 +33138,7 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L458" t="inlineStr">
@@ -33223,7 +33223,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -33265,7 +33265,7 @@
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L460" t="inlineStr">
@@ -33350,7 +33350,7 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L461" t="inlineStr">
@@ -33435,7 +33435,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L462" t="inlineStr">
@@ -33526,7 +33526,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L463" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -33653,7 +33653,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L465" t="inlineStr">
@@ -33738,7 +33738,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
@@ -33823,7 +33823,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -33914,7 +33914,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
@@ -33999,7 +33999,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -34041,7 +34041,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
@@ -34126,7 +34126,7 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L471" t="inlineStr">
@@ -34211,7 +34211,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
@@ -34387,7 +34387,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
@@ -34429,7 +34429,7 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L475" t="inlineStr">
@@ -34514,7 +34514,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
@@ -34599,7 +34599,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L477" t="inlineStr">
@@ -34690,7 +34690,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L478" t="inlineStr">
@@ -34775,7 +34775,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -34817,7 +34817,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L480" t="inlineStr">
@@ -34902,7 +34902,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L481" t="inlineStr">
@@ -34987,7 +34987,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L482" t="inlineStr">
@@ -35078,7 +35078,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L483" t="inlineStr">
@@ -35163,7 +35163,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L485" t="inlineStr">
@@ -35290,7 +35290,7 @@
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L486" t="inlineStr">
@@ -35375,7 +35375,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L487" t="inlineStr">
@@ -35466,7 +35466,7 @@
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
@@ -35551,7 +35551,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -35593,7 +35593,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L490" t="inlineStr">
@@ -35678,7 +35678,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
@@ -35763,7 +35763,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L492" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L493" t="inlineStr">
@@ -35939,7 +35939,7 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
@@ -35981,7 +35981,7 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
@@ -36066,7 +36066,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -36151,7 +36151,7 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L497" t="inlineStr">
@@ -36242,7 +36242,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L498" t="inlineStr">
@@ -36327,7 +36327,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -36369,7 +36369,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -36454,7 +36454,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -36539,7 +36539,7 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
@@ -36630,7 +36630,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L503" t="inlineStr">
@@ -36715,7 +36715,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -36757,7 +36757,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
@@ -36842,7 +36842,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L506" t="inlineStr">
@@ -36927,7 +36927,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
@@ -37018,7 +37018,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -37103,7 +37103,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -37145,7 +37145,7 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
@@ -37230,7 +37230,7 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L511" t="inlineStr">
@@ -37315,7 +37315,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L512" t="inlineStr">
@@ -37406,7 +37406,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L513" t="inlineStr">
@@ -37491,7 +37491,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L515" t="inlineStr">
@@ -37618,7 +37618,7 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L516" t="inlineStr">
@@ -37703,7 +37703,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
@@ -37794,7 +37794,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
@@ -37879,7 +37879,7 @@
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -37921,7 +37921,7 @@
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L520" t="inlineStr">
@@ -38006,7 +38006,7 @@
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
@@ -38091,7 +38091,7 @@
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
@@ -38182,7 +38182,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L523" t="inlineStr">
@@ -38267,7 +38267,7 @@
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -38309,7 +38309,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L525" t="inlineStr">
@@ -38394,7 +38394,7 @@
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L526" t="inlineStr">
@@ -38479,7 +38479,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
@@ -38570,7 +38570,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
@@ -38655,7 +38655,7 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>DCC_class</t>
+          <t>dcc_class</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -38697,7 +38697,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>DCC_limit</t>
+          <t>dcc_limit</t>
         </is>
       </c>
       <c r="L530" t="inlineStr">
@@ -38782,7 +38782,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>DCC_min learning</t>
+          <t>dcc_learning_min</t>
         </is>
       </c>
       <c r="L531" t="inlineStr">
@@ -38867,7 +38867,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>DCC_capacity_1</t>
+          <t>dcc_capacity_1</t>
         </is>
       </c>
       <c r="L532" t="inlineStr">
@@ -38952,7 +38952,7 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>DCC_progress ratio_1</t>
+          <t>dcc_progress_ratio_1</t>
         </is>
       </c>
       <c r="L533" t="inlineStr">
